--- a/项目进度追踪.xlsx
+++ b/项目进度追踪.xlsx
@@ -56,7 +56,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -105,6 +105,12 @@
         <bgColor rgb="0090EE90"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -124,7 +130,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -152,6 +158,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1653,7 +1662,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1959,6 +1968,458 @@
           <t>避免大屏看板每次请求都走全表扫描聚合</t>
         </is>
       </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>OPT-006</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>健康科普</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>隐私保护</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>P0-紧急</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>原方案：体验后生成"未来10年医疗费用预估账单"并做经济对比</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>已采纳建议，移除此功能。用户资产属于隐私，不应推测。替代方案待后续设计</t>
+        </is>
+      </c>
+      <c r="H7" s="10" t="inlineStr">
+        <is>
+          <t>已采纳</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>已同步更新开发文档4.3.3和面试框架7.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>OPT-007</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>预警引擎</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>功能完善</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>P1-高</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>预警升降级机制未定义；预警去重未考虑；同一用户规则冲突无处理</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>1.增加升降级策略：绿→留观,红→橙需人工确认逐级降；2.引入24h冷静期防重复预警；3.规则优先级：红&gt;橙&gt;黄&gt;绿，同用户只保留最高级别</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>待讨论</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr"/>
+      <c r="J8" s="5" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>OPT-008</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>预警引擎</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>数据来源</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>P1-高</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>体检数据/可穿戴设备数据/家属反馈的接入方式、格式、时效性全未定义</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>MVP阶段先用人工录入+定时任务模拟兜底(LN-001技术债)，后续对接卫健委API/设备SDK</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>待讨论</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr"/>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>标注为技术债</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>OPT-009</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>多端协同</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>离线场景</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>P1-高</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>社区医生上门访视时常无网络，拍照上传必然失败</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>前端增加离线队列：照片本地暂存IndexedDB，网络恢复自动重传，上传成功前任务状态为"待同步"</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>待讨论</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr"/>
+      <c r="J10" s="5" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>OPT-010</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>多端协同</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>防伪需求</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>P1-高</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>补贴消费留痕仅"拍照上传"，无时间戳+GPS水印，存在造假风险</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>照片强制嵌入时间+GPS+上传者ID水印；服务器端校验GPS与任务地点偏差</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>待讨论</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr"/>
+      <c r="J11" s="5" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>OPT-011</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>多端协同</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>任务流转</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>P2-中</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>任务转让/转派机制缺失，医生请假任务积压</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>增加"任务池"+"主动认领"：超24h未领任务自动回池</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>待讨论</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr"/>
+      <c r="J12" s="5" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>OPT-012</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>健康教育</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>心理安全</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>P0-紧急</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>疾病体验模块无心理安全阀，焦虑症/疑病症用户体验后可能应激</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>体验前增加PHQ-9/GAD-7快速筛查；体验中每3分钟弹出"随时退出"按钮；体验后自动跳转心理支持频道</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>待讨论</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr"/>
+      <c r="J13" s="5" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>OPT-013</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>健康教育</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>内容审核</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>P1-高</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>社区内容无审核机制，匿名问答可能被滥用</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>MVP阶段敏感词过滤+人工抽查；后期接AI内容审核API</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="inlineStr">
+        <is>
+          <t>待讨论</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr"/>
+      <c r="J14" s="5" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>OPT-014</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>健康教育</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>推送策略</t>
+        </is>
+      </c>
+      <c r="E15" s="8" t="inlineStr">
+        <is>
+          <t>P2-中</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>科普推送仅按健康数据匹配，刚诊断即推科普可能引发恐慌</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>增加"情绪感知"维度：诊断后3天内只推正向心理支持，第4天起逐步引入科普</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>待讨论</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr"/>
+      <c r="J15" s="5" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>OPT-015</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>商业模式</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>MVP策略</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>P1-高</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>B端/C端/G端收入都建立在"已有大量数据"前提上，MVP期收入为零</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>MVP阶段先与一个社区合作公益试点(0收入)，3-6个月积累数据后，拿着真实效果数据去谈B端和G端</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>待讨论</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr"/>
+      <c r="J16" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:J6"/>
@@ -2103,7 +2564,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2474,6 +2935,58 @@
       </c>
       <c r="J7" s="5" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>TODO-007</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>健康教育</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>功能替代</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>P2-中</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>疾病体验模块的"经济对比"功能已移除，需设计替代方案</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>方向：不做任何经济推测，聚焦于健康行动清单的个性化推荐（运动/饮食/就医/保险建议）</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>未开始</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>待定</t>
+        </is>
+      </c>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>隐私优于恐吓</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:J7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/项目进度追踪.xlsx
+++ b/项目进度追踪.xlsx
@@ -130,7 +130,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -161,6 +161,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -615,9 +618,9 @@
           <t>P0-紧急</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr">
-        <is>
-          <t>进行中</t>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>已完成</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -635,7 +638,11 @@
           <t>2026-05-20</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr"/>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
       <c r="J2" s="5" t="inlineStr">
         <is>
           <t>utf8mb4, 3306端口, SSL强制连接</t>
@@ -734,7 +741,7 @@
       <c r="I4" s="2" t="inlineStr"/>
       <c r="J4" s="5" t="inlineStr">
         <is>
-          <t>配置存入Nacos, tx-group创建</t>
+          <t>沙箱无Maven网络，代码已就绪待联网编译</t>
         </is>
       </c>
     </row>
@@ -782,7 +789,7 @@
       <c r="I5" s="2" t="inlineStr"/>
       <c r="J5" s="5" t="inlineStr">
         <is>
-          <t>规则持久化至Nacos</t>
+          <t>沙箱无Maven网络，代码已就绪待联网编译</t>
         </is>
       </c>
     </row>
@@ -807,9 +814,9 @@
           <t>P1-高</t>
         </is>
       </c>
-      <c r="E6" s="6" t="inlineStr">
-        <is>
-          <t>未开始</t>
+      <c r="E6" s="11" t="inlineStr">
+        <is>
+          <t>已完成</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -827,7 +834,11 @@
           <t>2026-05-21</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr"/>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
       <c r="J6" s="5" t="inlineStr">
         <is>
           <t>分布式锁、缓存预热</t>
@@ -855,9 +866,9 @@
           <t>P0-紧急</t>
         </is>
       </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>未开始</t>
+      <c r="E7" s="11" t="inlineStr">
+        <is>
+          <t>已完成</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -875,7 +886,11 @@
           <t>2026-05-21</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr"/>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
       <c r="J7" s="5" t="inlineStr">
         <is>
           <t>统一依赖管理、公共模块抽取</t>
@@ -903,9 +918,9 @@
           <t>P1-高</t>
         </is>
       </c>
-      <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t>未开始</t>
+      <c r="E8" s="11" t="inlineStr">
+        <is>
+          <t>已完成</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -923,7 +938,11 @@
           <t>2026-05-23</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr"/>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
       <c r="J8" s="5" t="inlineStr">
         <is>
           <t>路由规则存Nacos, JWT鉴权</t>
@@ -1191,9 +1210,9 @@
           <t>P2-中</t>
         </is>
       </c>
-      <c r="E14" s="6" t="inlineStr">
-        <is>
-          <t>未开始</t>
+      <c r="E14" s="11" t="inlineStr">
+        <is>
+          <t>已完成</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1211,7 +1230,11 @@
           <t>2026-06-03</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr"/>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
       <c r="J14" s="5" t="inlineStr">
         <is>
           <t>数据聚合、报表导出</t>
@@ -1239,9 +1262,9 @@
           <t>P1-高</t>
         </is>
       </c>
-      <c r="E15" s="6" t="inlineStr">
-        <is>
-          <t>未开始</t>
+      <c r="E15" s="11" t="inlineStr">
+        <is>
+          <t>已完成</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1259,7 +1282,11 @@
           <t>2026-05-23</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr"/>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
       <c r="J15" s="5" t="inlineStr">
         <is>
           <t>Vite, Element Plus, TypeScript</t>
@@ -1287,9 +1314,9 @@
           <t>P1-高</t>
         </is>
       </c>
-      <c r="E16" s="6" t="inlineStr">
-        <is>
-          <t>未开始</t>
+      <c r="E16" s="11" t="inlineStr">
+        <is>
+          <t>已完成</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1307,7 +1334,11 @@
           <t>2026-05-24</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr"/>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
       <c r="J16" s="5" t="inlineStr">
         <is>
           <t>拦截器、Token注入</t>
@@ -1383,9 +1414,9 @@
           <t>P2-中</t>
         </is>
       </c>
-      <c r="E18" s="6" t="inlineStr">
-        <is>
-          <t>未开始</t>
+      <c r="E18" s="11" t="inlineStr">
+        <is>
+          <t>已完成</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1434,11 @@
           <t>2026-06-02</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr"/>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
       <c r="J18" s="5" t="inlineStr">
         <is>
           <t>监管看板、任务分配</t>
